--- a/Roguelike-Deckbuilder/Assets/Config/Excel/MapConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/MapConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425ED61E-547E-4B8E-A187-648D3510CEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E99E21-EB7F-4BDD-8722-4E0F6EA370DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -663,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -759,7 +759,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -785,19 +785,19 @@
         <v>15</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>10</v>
-      </c>
-      <c r="F5" s="1">
-        <v>15</v>
       </c>
       <c r="G5" s="1">
         <v>10</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -811,19 +811,19 @@
         <v>16</v>
       </c>
       <c r="D6" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E6" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>10</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -837,19 +837,19 @@
         <v>17</v>
       </c>
       <c r="D7" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1">
         <v>30</v>
       </c>
       <c r="F7" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>10</v>
       </c>
       <c r="H7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -860,21 +860,125 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1">
+        <v>60</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1">
+        <v>60</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/MapConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/MapConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E99E21-EB7F-4BDD-8722-4E0F6EA370DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C790301A-028D-4630-B085-B2A394DBAE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,6 +132,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -785,10 +786,10 @@
         <v>15</v>
       </c>
       <c r="D5" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1">
         <v>10</v>
@@ -811,10 +812,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="1">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
@@ -837,7 +838,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1">
         <v>30</v>
@@ -863,10 +864,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1">
         <v>15</v>
@@ -889,10 +890,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -915,10 +916,10 @@
         <v>16</v>
       </c>
       <c r="D10" s="1">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1">
         <v>10</v>
